--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Coviran Granada.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Coviran Granada.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2469.479999999999</v>
+        <v>2627.959999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2473.34</v>
+        <v>2629.72</v>
       </c>
       <c r="D2" t="n">
-        <v>107.0212748752699</v>
+        <v>108.3005034756552</v>
       </c>
       <c r="E2" t="n">
-        <v>118.6250171832421</v>
+        <v>119.8986964391646</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5116580310880829</v>
+        <v>0.5206210577389617</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1713581025854281</v>
+        <v>0.1699854298203011</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2875112309074573</v>
+        <v>0.2870528109028961</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3481865284974093</v>
+        <v>0.3406113537117904</v>
       </c>
       <c r="J2" t="n">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="L2" t="n">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="M2" t="n">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="N2" t="n">
-        <v>1079</v>
+        <v>1148</v>
       </c>
       <c r="O2" t="n">
-        <v>1453</v>
+        <v>1541</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7528497409326425</v>
+        <v>0.747695293546822</v>
       </c>
       <c r="Q2" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="R2" t="n">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1813471502590674</v>
+        <v>0.1790393013100437</v>
       </c>
       <c r="T2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="U2" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1103626943005181</v>
+        <v>0.1096555070354197</v>
       </c>
       <c r="W2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X2" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.07253886010362694</v>
+        <v>0.07083939835031539</v>
       </c>
       <c r="Z2" t="n">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="AA2" t="n">
-        <v>641</v>
+        <v>688</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3321243523316062</v>
+        <v>0.3338185346918972</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7426015141087405</v>
+        <v>0.7449707981829981</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3371428571428571</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.331858407079646</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3493150684931507</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3291731669266771</v>
+        <v>0.3386627906976744</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.485203028217481</v>
+        <v>1.489941596365996</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6637168141592921</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.002560819462228</v>
+        <v>1.02158273381295</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8552971576227391</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.975</v>
+        <v>0.9614243323442137</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.508928571428571</v>
+        <v>1.523809523809524</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.997907949790795</v>
+        <v>1.031746031746032</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.03765690376569</v>
+        <v>4.089285714285714</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.035564853556485</v>
+        <v>5.121031746031746</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.17124999999997</v>
+        <v>77.29294117647056</v>
       </c>
       <c r="C3" t="n">
-        <v>77.29187499999999</v>
+        <v>77.34470588235294</v>
       </c>
       <c r="D3" t="n">
-        <v>107.0212748752699</v>
+        <v>108.3005034756552</v>
       </c>
       <c r="E3" t="n">
-        <v>118.6250171832421</v>
+        <v>119.8986964391646</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5116580310880829</v>
+        <v>0.5206210577389617</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1713581025854281</v>
+        <v>0.1699854298203011</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2875112309074573</v>
+        <v>0.2870528109028961</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3481865284974093</v>
+        <v>0.3406113537117904</v>
       </c>
       <c r="J3" t="n">
-        <v>10.34375</v>
+        <v>10.38235294117647</v>
       </c>
       <c r="K3" t="n">
-        <v>9.75</v>
+        <v>9.529411764705882</v>
       </c>
       <c r="L3" t="n">
-        <v>5.28125</v>
+        <v>5.647058823529412</v>
       </c>
       <c r="M3" t="n">
-        <v>13.75</v>
+        <v>13.61764705882353</v>
       </c>
       <c r="N3" t="n">
-        <v>33.71875</v>
+        <v>33.76470588235294</v>
       </c>
       <c r="O3" t="n">
-        <v>45.40625</v>
+        <v>45.3235294117647</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7528497409326425</v>
+        <v>0.7476952935468218</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6875</v>
+        <v>3.705882352941177</v>
       </c>
       <c r="R3" t="n">
-        <v>10.9375</v>
+        <v>10.85294117647059</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1813471502590674</v>
+        <v>0.1790393013100437</v>
       </c>
       <c r="T3" t="n">
-        <v>2.21875</v>
+        <v>2.205882352941177</v>
       </c>
       <c r="U3" t="n">
-        <v>6.65625</v>
+        <v>6.647058823529412</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1103626943005181</v>
+        <v>0.1096555070354197</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5625</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>4.375</v>
+        <v>4.294117647058823</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.07253886010362694</v>
+        <v>0.07083939835031539</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.59375</v>
+        <v>6.852941176470588</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.03125</v>
+        <v>20.23529411764706</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3321243523316062</v>
+        <v>0.3338185346918972</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7426015141087405</v>
+        <v>0.7449707981829982</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3371428571428571</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.331858407079646</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3493150684931507</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3291731669266771</v>
+        <v>0.3386627906976744</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.485203028217481</v>
+        <v>1.489941596365996</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6637168141592921</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.002560819462228</v>
+        <v>1.02158273381295</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8552971576227391</v>
+        <v>0.8694581280788177</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.975</v>
+        <v>0.9614243323442137</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.508928571428571</v>
+        <v>1.523809523809524</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.997907949790795</v>
+        <v>1.031746031746032</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.03765690376569</v>
+        <v>4.089285714285714</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.035564853556485</v>
+        <v>5.121031746031745</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2477.2</v>
+        <v>2631.48</v>
       </c>
       <c r="C4" t="n">
-        <v>2473.34</v>
+        <v>2629.72</v>
       </c>
       <c r="D4" t="n">
-        <v>118.6250171832421</v>
+        <v>119.8986964391646</v>
       </c>
       <c r="E4" t="n">
-        <v>107.0212748752699</v>
+        <v>108.3005034756552</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5579878900791803</v>
+        <v>0.5637554585152839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1355421686746988</v>
+        <v>0.1338396824768912</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3289817232375979</v>
+        <v>0.3314097279472383</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2505822077317187</v>
+        <v>0.2493449781659389</v>
       </c>
       <c r="J4" t="n">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="K4" t="n">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="L4" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="M4" t="n">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="N4" t="n">
-        <v>1015</v>
+        <v>1083</v>
       </c>
       <c r="O4" t="n">
-        <v>1372</v>
+        <v>1456</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6390312063344201</v>
+        <v>0.6358078602620088</v>
       </c>
       <c r="Q4" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="R4" t="n">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="S4" t="n">
-        <v>0.159757801583605</v>
+        <v>0.1585152838427948</v>
       </c>
       <c r="T4" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="U4" t="n">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1145784816022357</v>
+        <v>0.1139737991266375</v>
       </c>
       <c r="W4" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="X4" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1006054960409874</v>
+        <v>0.09868995633187773</v>
       </c>
       <c r="Z4" t="n">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="AA4" t="n">
-        <v>700</v>
+        <v>751</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3260363297624592</v>
+        <v>0.3279475982532751</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7397959183673469</v>
+        <v>0.7438186813186813</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4606413994169096</v>
+        <v>0.4517906336088154</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3373983739837398</v>
+        <v>0.3448275862068966</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.411504424778761</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3314285714285714</v>
+        <v>0.3422103861517976</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.479591836734694</v>
+        <v>1.487637362637363</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6747967479674797</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.048034934497817</v>
+        <v>1.074718526100307</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.801255230125523</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.007936507936508</v>
+        <v>1.014925373134328</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.671641791044776</v>
+        <v>1.681159420289855</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.467700258397933</v>
+        <v>1.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.547803617571059</v>
+        <v>5.640394088669951</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.015503875968992</v>
+        <v>7.140394088669951</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.41250000000001</v>
+        <v>77.3964705882353</v>
       </c>
       <c r="C5" t="n">
-        <v>77.29187499999999</v>
+        <v>77.34470588235294</v>
       </c>
       <c r="D5" t="n">
-        <v>118.6250171832421</v>
+        <v>119.8986964391646</v>
       </c>
       <c r="E5" t="n">
-        <v>107.0212748752699</v>
+        <v>108.3005034756552</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5579878900791803</v>
+        <v>0.5637554585152839</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1355421686746988</v>
+        <v>0.1338396824768913</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3289817232375979</v>
+        <v>0.3314097279472383</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2505822077317187</v>
+        <v>0.2493449781659389</v>
       </c>
       <c r="J5" t="n">
-        <v>11.96875</v>
+        <v>11.91176470588235</v>
       </c>
       <c r="K5" t="n">
-        <v>11.90625</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>6.823529411764706</v>
       </c>
       <c r="M5" t="n">
-        <v>11.03125</v>
+        <v>10.91176470588235</v>
       </c>
       <c r="N5" t="n">
-        <v>31.71875</v>
+        <v>31.85294117647059</v>
       </c>
       <c r="O5" t="n">
-        <v>42.875</v>
+        <v>42.8235294117647</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6390312063344201</v>
+        <v>0.6358078602620088</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.9375</v>
+        <v>4.823529411764706</v>
       </c>
       <c r="R5" t="n">
-        <v>10.71875</v>
+        <v>10.67647058823529</v>
       </c>
       <c r="S5" t="n">
-        <v>0.159757801583605</v>
+        <v>0.1585152838427948</v>
       </c>
       <c r="T5" t="n">
-        <v>2.59375</v>
+        <v>2.647058823529412</v>
       </c>
       <c r="U5" t="n">
-        <v>7.6875</v>
+        <v>7.676470588235294</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1145784816022357</v>
+        <v>0.1139737991266376</v>
       </c>
       <c r="W5" t="n">
-        <v>2.75</v>
+        <v>2.735294117647059</v>
       </c>
       <c r="X5" t="n">
-        <v>6.75</v>
+        <v>6.647058823529412</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1006054960409874</v>
+        <v>0.09868995633187774</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.25</v>
+        <v>7.558823529411764</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.875</v>
+        <v>22.08823529411765</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3260363297624592</v>
+        <v>0.3279475982532752</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7397959183673469</v>
+        <v>0.7438186813186813</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4606413994169096</v>
+        <v>0.4517906336088154</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3373983739837398</v>
+        <v>0.3448275862068965</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.411504424778761</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3314285714285714</v>
+        <v>0.3422103861517976</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.479591836734694</v>
+        <v>1.487637362637363</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6747967479674797</v>
+        <v>0.689655172413793</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.048034934497817</v>
+        <v>1.074718526100307</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.801255230125523</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.007936507936508</v>
+        <v>1.014925373134328</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.671641791044776</v>
+        <v>1.681159420289855</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.467700258397933</v>
+        <v>1.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.547803617571059</v>
+        <v>5.64039408866995</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.015503875968992</v>
+        <v>7.140394088669949</v>
       </c>
     </row>
     <row r="7">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I9" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J9" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L9" t="n">
         <v>12</v>
       </c>
       <c r="M9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N9" t="n">
         <v>6</v>
@@ -1620,19 +1620,19 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="R9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T9" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="U9" t="n">
         <v>25</v>
@@ -1647,31 +1647,31 @@
         <v>7</v>
       </c>
       <c r="Y9" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Z9" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.66</v>
+        <v>0.663</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.382</v>
+        <v>0.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="AH9" t="n">
         <v>3</v>
@@ -1683,51 +1683,51 @@
         <v>0.429</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AL9" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.375</v>
+        <v>0.384</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>660:01</t>
+          <t>699:35</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>246.08</v>
+        <v>260.96</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.5</v>
+        <v>0.519</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.542</v>
+        <v>0.556</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.89</v>
+        <v>0.908</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.179</v>
+        <v>0.184</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.237</v>
+        <v>0.23</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.932</v>
+        <v>1.854</v>
       </c>
       <c r="AV9" t="n">
         <v>0.172</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.056</v>
+        <v>0.06</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.108</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="10">
@@ -1886,7 +1886,7 @@
         <v>0.04</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="11">
@@ -1896,16 +1896,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1914,19 +1914,19 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
+        <v>39</v>
+      </c>
+      <c r="I11" t="n">
+        <v>63</v>
+      </c>
+      <c r="J11" t="n">
+        <v>19</v>
+      </c>
+      <c r="K11" t="n">
+        <v>79</v>
+      </c>
+      <c r="L11" t="n">
         <v>37</v>
-      </c>
-      <c r="I11" t="n">
-        <v>55</v>
-      </c>
-      <c r="J11" t="n">
-        <v>18</v>
-      </c>
-      <c r="K11" t="n">
-        <v>75</v>
-      </c>
-      <c r="L11" t="n">
-        <v>36</v>
       </c>
       <c r="M11" t="n">
         <v>10</v>
@@ -1938,19 +1938,19 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R11" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="S11" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="T11" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="U11" t="n">
         <v>16</v>
@@ -1959,28 +1959,28 @@
         <v>28</v>
       </c>
       <c r="W11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="Z11" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.714</v>
+        <v>0.694</v>
       </c>
       <c r="AB11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.5</v>
+        <v>0.516</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2011,41 +2011,41 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>592:29</t>
+          <t>624:04</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>167.2</v>
+        <v>179.72</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.667</v>
+        <v>0.678</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.106</v>
+        <v>1.107</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.191</v>
+        <v>0.189</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX11" t="n">
         <v>0.142</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="12">
@@ -2055,100 +2055,100 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="H12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J12" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L12" t="n">
         <v>5</v>
       </c>
       <c r="M12" t="n">
+        <v>26</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>71</v>
+      </c>
+      <c r="R12" t="n">
+        <v>65</v>
+      </c>
+      <c r="S12" t="n">
+        <v>97</v>
+      </c>
+      <c r="T12" t="n">
+        <v>298</v>
+      </c>
+      <c r="U12" t="n">
+        <v>48</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>21</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>92</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AE12" t="n">
         <v>23</v>
       </c>
-      <c r="N12" t="n">
-        <v>8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>66</v>
-      </c>
-      <c r="R12" t="n">
-        <v>61</v>
-      </c>
-      <c r="S12" t="n">
-        <v>91</v>
-      </c>
-      <c r="T12" t="n">
-        <v>267</v>
-      </c>
-      <c r="U12" t="n">
-        <v>46</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>19</v>
-      </c>
-      <c r="X12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>89</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>119</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.748</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>33</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>21</v>
-      </c>
       <c r="AF12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.467</v>
+        <v>0.469</v>
       </c>
       <c r="AH12" t="n">
         <v>2</v>
@@ -2160,51 +2160,51 @@
         <v>0.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AL12" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.297</v>
+        <v>0.308</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>637:01</t>
+          <t>687:48</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>332.72</v>
+        <v>355.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.432</v>
+        <v>0.443</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.512</v>
+        <v>0.518</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.821</v>
+        <v>0.83</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.198</v>
+        <v>0.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.333</v>
+        <v>0.318</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.394</v>
+        <v>1.465</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.241</v>
+        <v>0.238</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.119</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="13">
@@ -2214,16 +2214,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
         <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2283,10 +2283,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
         <v>1</v>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>02:59</t>
+          <t>04:26</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>3.32</v>
+        <v>4.32</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.753</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.506</v>
+        <v>1.62</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="n">
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.513</v>
+        <v>0.449</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -2363,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="14">
@@ -2373,40 +2373,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G14" t="n">
+        <v>62</v>
+      </c>
+      <c r="H14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I14" t="n">
+        <v>44</v>
+      </c>
+      <c r="J14" t="n">
         <v>22</v>
       </c>
-      <c r="G14" t="n">
-        <v>55</v>
-      </c>
-      <c r="H14" t="n">
-        <v>31</v>
-      </c>
-      <c r="I14" t="n">
-        <v>41</v>
-      </c>
-      <c r="J14" t="n">
-        <v>20</v>
-      </c>
       <c r="K14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L14" t="n">
         <v>14</v>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N14" t="n">
         <v>12</v>
@@ -2421,19 +2421,19 @@
         <v>15</v>
       </c>
       <c r="R14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="T14" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="U14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W14" t="n">
         <v>9</v>
@@ -2442,84 +2442,84 @@
         <v>7</v>
       </c>
       <c r="Y14" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="Z14" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.743</v>
+        <v>0.753</v>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.167</v>
+        <v>0.211</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
       </c>
       <c r="AF14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI14" t="n">
         <v>20</v>
       </c>
-      <c r="AG14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>17</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>0.412</v>
+        <v>0.4</v>
       </c>
       <c r="AK14" t="n">
         <v>15</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.395</v>
+        <v>0.357</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>385:49</t>
+          <t>434:20</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>155.04</v>
+        <v>169.36</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.5</v>
+        <v>0.493</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.546</v>
+        <v>0.541</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.987</v>
+        <v>0.986</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.097</v>
+        <v>0.089</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.254</v>
+        <v>0.252</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.333</v>
+        <v>1.467</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.185</v>
+        <v>0.18</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.104</v>
+        <v>0.101</v>
       </c>
       <c r="AY14" t="n">
         <v>0.025</v>
@@ -2678,10 +2678,10 @@
         <v>0.033</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="16">
@@ -2834,13 +2834,13 @@
         <v>0.166</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="17">
@@ -2850,40 +2850,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="D17" t="n">
+        <v>68</v>
+      </c>
+      <c r="E17" t="n">
+        <v>127</v>
+      </c>
+      <c r="F17" t="n">
+        <v>31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>85</v>
+      </c>
+      <c r="H17" t="n">
+        <v>22</v>
+      </c>
+      <c r="I17" t="n">
+        <v>32</v>
+      </c>
+      <c r="J17" t="n">
+        <v>27</v>
+      </c>
+      <c r="K17" t="n">
         <v>60</v>
-      </c>
-      <c r="E17" t="n">
-        <v>110</v>
-      </c>
-      <c r="F17" t="n">
-        <v>24</v>
-      </c>
-      <c r="G17" t="n">
-        <v>73</v>
-      </c>
-      <c r="H17" t="n">
-        <v>21</v>
-      </c>
-      <c r="I17" t="n">
-        <v>31</v>
-      </c>
-      <c r="J17" t="n">
-        <v>25</v>
-      </c>
-      <c r="K17" t="n">
-        <v>58</v>
       </c>
       <c r="L17" t="n">
         <v>17</v>
       </c>
       <c r="M17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N17" t="n">
         <v>9</v>
@@ -2892,58 +2892,58 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S17" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="U17" t="n">
         <v>22</v>
       </c>
       <c r="V17" t="n">
+        <v>32</v>
+      </c>
+      <c r="W17" t="n">
+        <v>28</v>
+      </c>
+      <c r="X17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF17" t="n">
         <v>30</v>
       </c>
-      <c r="W17" t="n">
-        <v>22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>79</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.772</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>26</v>
-      </c>
       <c r="AG17" t="n">
-        <v>0.231</v>
+        <v>0.233</v>
       </c>
       <c r="AH17" t="n">
         <v>4</v>
@@ -2955,48 +2955,48 @@
         <v>0.333</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.328</v>
+        <v>0.37</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>442:21</t>
+          <t>489:08</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>229.64</v>
+        <v>260.08</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.525</v>
+        <v>0.54</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.542</v>
+        <v>0.555</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.928</v>
+        <v>0.965</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.144</v>
+        <v>0.131</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.115</v>
+        <v>0.104</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.758</v>
+        <v>0.794</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.239</v>
+        <v>0.245</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.044</v>
+        <v>0.04</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.147</v>
+        <v>0.138</v>
       </c>
       <c r="AY17" t="n">
         <v>0.032</v>
@@ -3152,10 +3152,10 @@
         <v>0.18</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.112</v>
+        <v>0.113</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>51:17</t>
+          <t>51:24</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3308,7 +3308,7 @@
         <v>0.25</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
@@ -3327,22 +3327,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -3351,13 +3351,13 @@
         <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>8</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
@@ -3375,13 +3375,13 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U20" t="n">
         <v>3</v>
@@ -3396,13 +3396,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AB20" t="n">
         <v>1</v>
@@ -3426,10 +3426,10 @@
         <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AK20" t="n">
         <v>2</v>
@@ -3442,41 +3442,41 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>72:57</t>
+          <t>85:17</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>15.88</v>
+        <v>17.88</v>
       </c>
       <c r="AP20" t="n">
         <v>0.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.47</v>
+        <v>0.474</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.882</v>
+        <v>0.895</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.063</v>
+        <v>0.056</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.1</v>
+        <v>0.097</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.032</v>
+        <v>0.041</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.123</v>
+        <v>0.106</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="21">
@@ -3632,7 +3632,7 @@
         <v>0.017</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="AY21" t="n">
         <v>0.007</v>
@@ -3791,10 +3791,10 @@
         <v>0.019</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="23">
@@ -3804,82 +3804,82 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" t="n">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="D23" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F23" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H23" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I23" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J23" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K23" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L23" t="n">
         <v>24</v>
       </c>
       <c r="M23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="R23" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="S23" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="T23" t="n">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="U23" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="V23" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="W23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="X23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="Z23" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.803</v>
+        <v>0.802</v>
       </c>
       <c r="AB23" t="n">
         <v>8</v>
@@ -3894,10 +3894,10 @@
         <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.167</v>
+        <v>0.154</v>
       </c>
       <c r="AH23" t="n">
         <v>6</v>
@@ -3909,51 +3909,51 @@
         <v>0.375</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.328</v>
+        <v>0.343</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>475:24</t>
+          <t>500:16</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>246.6</v>
+        <v>261.8</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.532</v>
+        <v>0.546</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.595</v>
+        <v>0.605</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.977</v>
+        <v>0.997</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.322</v>
+        <v>0.319</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.864</v>
+        <v>0.913</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.239</v>
+        <v>0.241</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="24">
@@ -3963,34 +3963,34 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" t="n">
+        <v>109</v>
+      </c>
+      <c r="D24" t="n">
         <v>18</v>
       </c>
-      <c r="C24" t="n">
-        <v>88</v>
-      </c>
-      <c r="D24" t="n">
-        <v>15</v>
-      </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G24" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L24" t="n">
         <v>20</v>
@@ -4005,19 +4005,19 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R24" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T24" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="U24" t="n">
         <v>13</v>
@@ -4026,19 +4026,19 @@
         <v>16</v>
       </c>
       <c r="W24" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y24" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Z24" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.652</v>
+        <v>0.679</v>
       </c>
       <c r="AB24" t="n">
         <v>6</v>
@@ -4062,54 +4062,54 @@
         <v>2</v>
       </c>
       <c r="AI24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AK24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AL24" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.345</v>
+        <v>0.412</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>305:43</t>
+          <t>335:44</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>98.88</v>
+        <v>110.64</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.506</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.89</v>
+        <v>0.985</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.121</v>
+        <v>0.117</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.293</v>
+        <v>0.298</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.75</v>
+        <v>0.769</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.149</v>
+        <v>0.152</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.076</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.194</v>
+        <v>0.204</v>
       </c>
       <c r="AY24" t="n">
         <v>0.011</v>
@@ -4122,88 +4122,88 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>34</v>
+      </c>
+      <c r="C25" t="n">
+        <v>550</v>
+      </c>
+      <c r="D25" t="n">
+        <v>128</v>
+      </c>
+      <c r="E25" t="n">
+        <v>229</v>
+      </c>
+      <c r="F25" t="n">
+        <v>19</v>
+      </c>
+      <c r="G25" t="n">
+        <v>57</v>
+      </c>
+      <c r="H25" t="n">
+        <v>237</v>
+      </c>
+      <c r="I25" t="n">
+        <v>290</v>
+      </c>
+      <c r="J25" t="n">
+        <v>106</v>
+      </c>
+      <c r="K25" t="n">
+        <v>153</v>
+      </c>
+      <c r="L25" t="n">
+        <v>70</v>
+      </c>
+      <c r="M25" t="n">
+        <v>38</v>
+      </c>
+      <c r="N25" t="n">
+        <v>33</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>61</v>
+      </c>
+      <c r="R25" t="n">
+        <v>55</v>
+      </c>
+      <c r="S25" t="n">
+        <v>238</v>
+      </c>
+      <c r="T25" t="n">
+        <v>880</v>
+      </c>
+      <c r="U25" t="n">
+        <v>82</v>
+      </c>
+      <c r="V25" t="n">
+        <v>83</v>
+      </c>
+      <c r="W25" t="n">
+        <v>35</v>
+      </c>
+      <c r="X25" t="n">
         <v>32</v>
       </c>
-      <c r="C25" t="n">
-        <v>515</v>
-      </c>
-      <c r="D25" t="n">
-        <v>117</v>
-      </c>
-      <c r="E25" t="n">
-        <v>210</v>
-      </c>
-      <c r="F25" t="n">
-        <v>18</v>
-      </c>
-      <c r="G25" t="n">
-        <v>56</v>
-      </c>
-      <c r="H25" t="n">
-        <v>227</v>
-      </c>
-      <c r="I25" t="n">
-        <v>280</v>
-      </c>
-      <c r="J25" t="n">
-        <v>94</v>
-      </c>
-      <c r="K25" t="n">
-        <v>144</v>
-      </c>
-      <c r="L25" t="n">
-        <v>62</v>
-      </c>
-      <c r="M25" t="n">
-        <v>35</v>
-      </c>
-      <c r="N25" t="n">
-        <v>31</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>57</v>
-      </c>
-      <c r="R25" t="n">
-        <v>53</v>
-      </c>
-      <c r="S25" t="n">
-        <v>230</v>
-      </c>
-      <c r="T25" t="n">
-        <v>817</v>
-      </c>
-      <c r="U25" t="n">
-        <v>71</v>
-      </c>
-      <c r="V25" t="n">
-        <v>81</v>
-      </c>
-      <c r="W25" t="n">
-        <v>33</v>
-      </c>
-      <c r="X25" t="n">
-        <v>30</v>
-      </c>
       <c r="Y25" t="n">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="Z25" t="n">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.767</v>
+        <v>0.771</v>
       </c>
       <c r="AB25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AC25" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AD25" t="n">
         <v>0.328</v>
@@ -4212,10 +4212,10 @@
         <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="AH25" t="n">
         <v>2</v>
@@ -4227,51 +4227,51 @@
         <v>0.154</v>
       </c>
       <c r="AK25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL25" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.372</v>
+        <v>0.386</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>933:23</t>
+          <t>995:00</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>446.2</v>
+        <v>474.6</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.541</v>
+        <v>0.547</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.662</v>
+        <v>0.665</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.154</v>
+        <v>1.159</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.853</v>
+        <v>0.829</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.649</v>
+        <v>1.738</v>
       </c>
       <c r="AV25" t="n">
         <v>0.22</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.077</v>
+        <v>0.082</v>
       </c>
       <c r="AX25" t="n">
         <v>0.173</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.13</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="26">
@@ -4586,10 +4586,10 @@
         <v>0.098</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.278</v>
+        <v>0.28</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="28">
@@ -4599,16 +4599,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C28" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E28" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -4617,49 +4617,49 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I28" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
+        <v>27</v>
+      </c>
+      <c r="L28" t="n">
         <v>26</v>
-      </c>
-      <c r="L28" t="n">
-        <v>25</v>
       </c>
       <c r="M28" t="n">
         <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R28" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="S28" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="T28" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="U28" t="n">
         <v>10</v>
       </c>
       <c r="V28" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="W28" t="n">
         <v>4</v>
@@ -4668,13 +4668,13 @@
         <v>3</v>
       </c>
       <c r="Y28" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="Z28" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.776</v>
+        <v>0.787</v>
       </c>
       <c r="AB28" t="n">
         <v>5</v>
@@ -4714,38 +4714,38 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>289:42</t>
+          <t>308:46</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>94.44</v>
+        <v>102.64</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.735</v>
+        <v>0.755</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.756</v>
+        <v>0.773</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.144</v>
+        <v>1.169</v>
       </c>
       <c r="AS28" t="n">
         <v>0.244</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.735</v>
+        <v>0.755</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.478</v>
+        <v>0.48</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.15</v>
+        <v>0.153</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="AY28" t="n">
         <v>0.013</v>
@@ -4898,16 +4898,16 @@
         <v>0.615</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="AW29" t="n">
         <v>0.047</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.145</v>
+        <v>0.146</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -4917,40 +4917,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C30" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E30" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F30" t="n">
         <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
         <v>19</v>
       </c>
       <c r="L30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N30" t="n">
         <v>6</v>
@@ -4959,22 +4959,22 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R30" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="S30" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="T30" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V30" t="n">
         <v>8</v>
@@ -4986,84 +4986,84 @@
         <v>4</v>
       </c>
       <c r="Y30" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Z30" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.741</v>
+        <v>0.738</v>
       </c>
       <c r="AB30" t="n">
         <v>4</v>
       </c>
       <c r="AC30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.125</v>
+        <v>0.111</v>
       </c>
       <c r="AH30" t="n">
         <v>2</v>
       </c>
       <c r="AI30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AK30" t="n">
         <v>7</v>
       </c>
       <c r="AL30" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.206</v>
+        <v>0.184</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>257:47</t>
+          <t>291:05</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>130.64</v>
+        <v>141.52</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.397</v>
+        <v>0.375</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.464</v>
+        <v>0.441</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="AS30" t="n">
         <v>0.191</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.272</v>
+        <v>0.26</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.76</v>
+        <v>0.778</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.233</v>
+        <v>0.224</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.036</v>
+        <v>0.044</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.082</v>
+        <v>0.073</v>
       </c>
       <c r="AY30" t="n">
         <v>0.023</v>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -5103,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L31" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -5118,13 +5118,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -5235,150 +5235,150 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>2647</v>
+        <v>2848</v>
       </c>
       <c r="D32" t="n">
-        <v>596</v>
+        <v>647</v>
       </c>
       <c r="E32" t="n">
-        <v>1149</v>
+        <v>1227</v>
       </c>
       <c r="F32" t="n">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="G32" t="n">
-        <v>781</v>
+        <v>834</v>
       </c>
       <c r="H32" t="n">
-        <v>672</v>
+        <v>702</v>
       </c>
       <c r="I32" t="n">
-        <v>867</v>
+        <v>909</v>
       </c>
       <c r="J32" t="n">
-        <v>477</v>
+        <v>520</v>
       </c>
       <c r="K32" t="n">
-        <v>771</v>
+        <v>811</v>
       </c>
       <c r="L32" t="n">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="M32" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="N32" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="Q32" t="n">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="R32" t="n">
-        <v>749</v>
+        <v>787</v>
       </c>
       <c r="S32" t="n">
-        <v>748</v>
+        <v>789</v>
       </c>
       <c r="T32" t="n">
-        <v>2890</v>
+        <v>3119</v>
       </c>
       <c r="U32" t="n">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="V32" t="n">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="W32" t="n">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="X32" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="Y32" t="n">
-        <v>1079</v>
+        <v>1148</v>
       </c>
       <c r="Z32" t="n">
-        <v>1453</v>
+        <v>1541</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="AB32" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="AC32" t="n">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="AE32" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.333</v>
+        <v>0.332</v>
       </c>
       <c r="AH32" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AI32" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.357</v>
+        <v>0.349</v>
       </c>
       <c r="AK32" t="n">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="AL32" t="n">
-        <v>641</v>
+        <v>688</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.329</v>
+        <v>0.339</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>6425:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>2789.48</v>
+        <v>2964.96</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.512</v>
+        <v>0.521</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.949</v>
+        <v>0.961</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.348</v>
+        <v>0.341</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.998</v>
+        <v>1.032</v>
       </c>
       <c r="AV32" t="n">
         <v>0.2</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="AX32" t="n">
         <v>0.134</v>
@@ -5394,144 +5394,144 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>2934</v>
+        <v>3153</v>
       </c>
       <c r="D33" t="n">
-        <v>718</v>
+        <v>766</v>
       </c>
       <c r="E33" t="n">
-        <v>1231</v>
+        <v>1313</v>
       </c>
       <c r="F33" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="G33" t="n">
-        <v>916</v>
+        <v>977</v>
       </c>
       <c r="H33" t="n">
-        <v>538</v>
+        <v>571</v>
       </c>
       <c r="I33" t="n">
-        <v>730</v>
+        <v>767</v>
       </c>
       <c r="J33" t="n">
-        <v>568</v>
+        <v>609</v>
       </c>
       <c r="K33" t="n">
-        <v>793</v>
+        <v>837</v>
       </c>
       <c r="L33" t="n">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="M33" t="n">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="N33" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="Q33" t="n">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="R33" t="n">
-        <v>753</v>
+        <v>795</v>
       </c>
       <c r="S33" t="n">
-        <v>738</v>
+        <v>774</v>
       </c>
       <c r="T33" t="n">
-        <v>3428</v>
+        <v>3680</v>
       </c>
       <c r="U33" t="n">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="V33" t="n">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="W33" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="X33" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="Y33" t="n">
-        <v>1015</v>
+        <v>1083</v>
       </c>
       <c r="Z33" t="n">
-        <v>1372</v>
+        <v>1456</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.74</v>
+        <v>0.744</v>
       </c>
       <c r="AB33" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="AC33" t="n">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.461</v>
+        <v>0.452</v>
       </c>
       <c r="AE33" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="AF33" t="n">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.337</v>
+        <v>0.345</v>
       </c>
       <c r="AH33" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.407</v>
+        <v>0.412</v>
       </c>
       <c r="AK33" t="n">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="AL33" t="n">
-        <v>700</v>
+        <v>751</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.331</v>
+        <v>0.342</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>6425:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>2855.2</v>
+        <v>3033.48</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.594</v>
+        <v>0.6</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.028</v>
+        <v>1.039</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.136</v>
+        <v>0.134</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.251</v>
+        <v>0.249</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.468</v>
+        <v>1.5</v>
       </c>
       <c r="AV33" t="n">
         <v>0.2</v>
@@ -5540,7 +5540,7 @@
         <v>0.066</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.142</v>
+        <v>0.143</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -5769,156 +5769,156 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>6.844</v>
+        <v>6.971</v>
       </c>
       <c r="D36" t="n">
-        <v>1.219</v>
+        <v>1.265</v>
       </c>
       <c r="E36" t="n">
-        <v>2.812</v>
+        <v>2.765</v>
       </c>
       <c r="F36" t="n">
-        <v>1.031</v>
+        <v>1.059</v>
       </c>
       <c r="G36" t="n">
-        <v>2.719</v>
+        <v>2.735</v>
       </c>
       <c r="H36" t="n">
-        <v>1.312</v>
+        <v>1.265</v>
       </c>
       <c r="I36" t="n">
-        <v>1.781</v>
+        <v>1.735</v>
       </c>
       <c r="J36" t="n">
-        <v>2.656</v>
+        <v>2.618</v>
       </c>
       <c r="K36" t="n">
-        <v>1.031</v>
+        <v>1.088</v>
       </c>
       <c r="L36" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="M36" t="n">
-        <v>0.719</v>
+        <v>0.706</v>
       </c>
       <c r="N36" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.375</v>
+        <v>1.412</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.375</v>
+        <v>1.412</v>
       </c>
       <c r="R36" t="n">
-        <v>3.188</v>
+        <v>3.118</v>
       </c>
       <c r="S36" t="n">
-        <v>1.75</v>
+        <v>1.676</v>
       </c>
       <c r="T36" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="U36" t="n">
-        <v>0.781</v>
+        <v>0.735</v>
       </c>
       <c r="V36" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="W36" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="X36" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1.971</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.031</v>
+        <v>2.971</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.66</v>
+        <v>0.663</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.062</v>
+        <v>1.029</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.382</v>
+        <v>0.4</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.125</v>
+        <v>0.147</v>
       </c>
       <c r="AF36" t="n">
         <v>0.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.429</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.971</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.5</v>
+        <v>2.529</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.375</v>
+        <v>0.384</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>7.69</v>
+        <v>7.675</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.5</v>
+        <v>0.519</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.542</v>
+        <v>0.556</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.89</v>
+        <v>0.908</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.179</v>
+        <v>0.184</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.237</v>
+        <v>0.23</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.932</v>
+        <v>1.854</v>
       </c>
       <c r="AV36" t="n">
         <v>0.172</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.056</v>
+        <v>0.06</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.108</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="37">
@@ -6077,7 +6077,7 @@
         <v>0.04</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="38">
@@ -6087,16 +6087,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C38" t="n">
-        <v>5.968</v>
+        <v>6.03</v>
       </c>
       <c r="D38" t="n">
-        <v>2.387</v>
+        <v>2.424</v>
       </c>
       <c r="E38" t="n">
-        <v>3.581</v>
+        <v>3.576</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -6105,79 +6105,79 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.194</v>
+        <v>1.182</v>
       </c>
       <c r="I38" t="n">
-        <v>1.774</v>
+        <v>1.909</v>
       </c>
       <c r="J38" t="n">
-        <v>0.581</v>
+        <v>0.576</v>
       </c>
       <c r="K38" t="n">
-        <v>2.419</v>
+        <v>2.394</v>
       </c>
       <c r="L38" t="n">
-        <v>1.161</v>
+        <v>1.121</v>
       </c>
       <c r="M38" t="n">
-        <v>0.323</v>
+        <v>0.303</v>
       </c>
       <c r="N38" t="n">
-        <v>1.065</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.032</v>
+        <v>1.03</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.032</v>
+        <v>1.03</v>
       </c>
       <c r="R38" t="n">
-        <v>2.484</v>
+        <v>2.545</v>
       </c>
       <c r="S38" t="n">
-        <v>1.194</v>
+        <v>1.273</v>
       </c>
       <c r="T38" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="U38" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>3.091</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.455</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="AD38" t="n">
         <v>0.516</v>
       </c>
-      <c r="V38" t="n">
-        <v>0.903</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>3.065</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.968</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AE38" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="AG38" t="n">
         <v>0.333</v>
@@ -6202,41 +6202,41 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>5.394</v>
+        <v>5.446</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.667</v>
+        <v>0.678</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.106</v>
+        <v>1.107</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.191</v>
+        <v>0.189</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX38" t="n">
         <v>0.142</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="39">
@@ -6246,156 +6246,156 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C39" t="n">
-        <v>10.111</v>
+        <v>10.172</v>
       </c>
       <c r="D39" t="n">
-        <v>1.704</v>
+        <v>1.724</v>
       </c>
       <c r="E39" t="n">
-        <v>4.037</v>
+        <v>4.034</v>
       </c>
       <c r="F39" t="n">
-        <v>1.296</v>
+        <v>1.345</v>
       </c>
       <c r="G39" t="n">
-        <v>4.407</v>
+        <v>4.414</v>
       </c>
       <c r="H39" t="n">
-        <v>2.815</v>
+        <v>2.69</v>
       </c>
       <c r="I39" t="n">
-        <v>3.259</v>
+        <v>3.103</v>
       </c>
       <c r="J39" t="n">
-        <v>3.407</v>
+        <v>3.586</v>
       </c>
       <c r="K39" t="n">
-        <v>2.259</v>
+        <v>2.276</v>
       </c>
       <c r="L39" t="n">
-        <v>0.185</v>
+        <v>0.172</v>
       </c>
       <c r="M39" t="n">
-        <v>0.852</v>
+        <v>0.897</v>
       </c>
       <c r="N39" t="n">
-        <v>0.296</v>
+        <v>0.31</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.444</v>
+        <v>2.448</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.444</v>
+        <v>2.448</v>
       </c>
       <c r="R39" t="n">
-        <v>2.259</v>
+        <v>2.241</v>
       </c>
       <c r="S39" t="n">
-        <v>3.37</v>
+        <v>3.345</v>
       </c>
       <c r="T39" t="n">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="U39" t="n">
-        <v>1.704</v>
+        <v>1.655</v>
       </c>
       <c r="V39" t="n">
-        <v>0.185</v>
+        <v>0.241</v>
       </c>
       <c r="W39" t="n">
-        <v>0.704</v>
+        <v>0.724</v>
       </c>
       <c r="X39" t="n">
-        <v>0.444</v>
+        <v>0.448</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.296</v>
+        <v>3.172</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.407</v>
+        <v>4.207</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.748</v>
+        <v>0.754</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.444</v>
+        <v>0.448</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.222</v>
+        <v>1.241</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.364</v>
+        <v>0.361</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.778</v>
+        <v>0.793</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.667</v>
+        <v>1.69</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.467</v>
+        <v>0.469</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.296</v>
+        <v>0.276</v>
       </c>
       <c r="AJ39" t="n">
         <v>0.25</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.222</v>
+        <v>1.276</v>
       </c>
       <c r="AL39" t="n">
-        <v>4.111</v>
+        <v>4.138</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.297</v>
+        <v>0.308</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>23:43</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>12.323</v>
+        <v>12.262</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.432</v>
+        <v>0.443</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.512</v>
+        <v>0.518</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.821</v>
+        <v>0.83</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.198</v>
+        <v>0.2</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.333</v>
+        <v>0.318</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.394</v>
+        <v>1.465</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.241</v>
+        <v>0.238</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.143</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="40">
@@ -6405,31 +6405,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>0.286</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2</v>
+        <v>0.286</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6</v>
+        <v>0.429</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.429</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -6441,7 +6441,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6453,13 +6453,13 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="S40" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="T40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -6474,19 +6474,19 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="AA40" t="n">
         <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="AD40" t="n">
         <v>1</v>
@@ -6513,39 +6513,39 @@
         <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="AM40" t="n">
         <v>0</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>00:35</t>
+          <t>00:38</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>0.664</v>
+        <v>0.617</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.753</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.506</v>
+        <v>1.62</v>
       </c>
       <c r="AS40" t="n">
         <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="n">
         <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.513</v>
+        <v>0.449</v>
       </c>
       <c r="AW40" t="n">
         <v>0</v>
@@ -6554,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="41">
@@ -6564,156 +6564,156 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C41" t="n">
-        <v>10.2</v>
+        <v>9.824</v>
       </c>
       <c r="D41" t="n">
-        <v>1.867</v>
+        <v>1.882</v>
       </c>
       <c r="E41" t="n">
-        <v>4.467</v>
+        <v>4.294</v>
       </c>
       <c r="F41" t="n">
-        <v>1.467</v>
+        <v>1.353</v>
       </c>
       <c r="G41" t="n">
-        <v>3.667</v>
+        <v>3.647</v>
       </c>
       <c r="H41" t="n">
-        <v>2.067</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>2.733</v>
+        <v>2.588</v>
       </c>
       <c r="J41" t="n">
-        <v>1.333</v>
+        <v>1.294</v>
       </c>
       <c r="K41" t="n">
-        <v>2.4</v>
+        <v>2.294</v>
       </c>
       <c r="L41" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6</v>
+        <v>0.647</v>
       </c>
       <c r="N41" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>0.882</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0.882</v>
       </c>
       <c r="R41" t="n">
-        <v>2.8</v>
+        <v>2.706</v>
       </c>
       <c r="S41" t="n">
-        <v>2.333</v>
+        <v>2.235</v>
       </c>
       <c r="T41" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="U41" t="n">
         <v>1</v>
       </c>
       <c r="V41" t="n">
-        <v>1.067</v>
+        <v>1.059</v>
       </c>
       <c r="W41" t="n">
-        <v>0.6</v>
+        <v>0.529</v>
       </c>
       <c r="X41" t="n">
-        <v>0.467</v>
+        <v>0.412</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.467</v>
+        <v>3.412</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.667</v>
+        <v>4.529</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.743</v>
+        <v>0.753</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.2</v>
+        <v>0.235</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.2</v>
+        <v>1.118</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.167</v>
+        <v>0.211</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.267</v>
+        <v>0.235</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.333</v>
+        <v>1.235</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.467</v>
+        <v>0.471</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.133</v>
+        <v>1.176</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.412</v>
+        <v>0.4</v>
       </c>
       <c r="AK41" t="n">
-        <v>1</v>
+        <v>0.882</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.533</v>
+        <v>2.471</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.395</v>
+        <v>0.357</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>25:43</t>
+          <t>25:32</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>10.336</v>
+        <v>9.962</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.5</v>
+        <v>0.493</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.546</v>
+        <v>0.541</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.987</v>
+        <v>0.986</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.097</v>
+        <v>0.089</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.254</v>
+        <v>0.252</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.333</v>
+        <v>1.467</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.185</v>
+        <v>0.18</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.104</v>
+        <v>0.101</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="42">
@@ -6869,10 +6869,10 @@
         <v>0.033</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.068</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="43">
@@ -7025,13 +7025,13 @@
         <v>0.166</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="44">
@@ -7041,156 +7041,156 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C44" t="n">
-        <v>11.833</v>
+        <v>12.55</v>
       </c>
       <c r="D44" t="n">
-        <v>3.333</v>
+        <v>3.4</v>
       </c>
       <c r="E44" t="n">
-        <v>6.111</v>
+        <v>6.35</v>
       </c>
       <c r="F44" t="n">
-        <v>1.333</v>
+        <v>1.55</v>
       </c>
       <c r="G44" t="n">
-        <v>4.056</v>
+        <v>4.25</v>
       </c>
       <c r="H44" t="n">
-        <v>1.167</v>
+        <v>1.1</v>
       </c>
       <c r="I44" t="n">
-        <v>1.722</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
-        <v>1.389</v>
+        <v>1.35</v>
       </c>
       <c r="K44" t="n">
-        <v>3.222</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
-        <v>0.944</v>
+        <v>0.85</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.833</v>
+        <v>1.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.833</v>
+        <v>1.7</v>
       </c>
       <c r="R44" t="n">
-        <v>2.556</v>
+        <v>2.35</v>
       </c>
       <c r="S44" t="n">
-        <v>1.444</v>
+        <v>1.5</v>
       </c>
       <c r="T44" t="n">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="U44" t="n">
-        <v>1.222</v>
+        <v>1.1</v>
       </c>
       <c r="V44" t="n">
-        <v>1.667</v>
+        <v>1.6</v>
       </c>
       <c r="W44" t="n">
-        <v>1.222</v>
+        <v>1.4</v>
       </c>
       <c r="X44" t="n">
-        <v>0.611</v>
+        <v>0.7</v>
       </c>
       <c r="Y44" t="n">
-        <v>3.389</v>
+        <v>3.35</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.389</v>
+        <v>4.35</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.778</v>
+        <v>0.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.389</v>
+        <v>0.381</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.444</v>
+        <v>1.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.231</v>
+        <v>0.233</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AJ44" t="n">
         <v>0.333</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.111</v>
+        <v>1.35</v>
       </c>
       <c r="AL44" t="n">
-        <v>3.389</v>
+        <v>3.65</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.328</v>
+        <v>0.37</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>24:34</t>
+          <t>24:27</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>12.758</v>
+        <v>13.004</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.525</v>
+        <v>0.54</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.542</v>
+        <v>0.555</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.928</v>
+        <v>0.965</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.144</v>
+        <v>0.131</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.115</v>
+        <v>0.104</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.758</v>
+        <v>0.794</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.239</v>
+        <v>0.245</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.044</v>
+        <v>0.04</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.147</v>
+        <v>0.138</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="45">
@@ -7343,10 +7343,10 @@
         <v>0.18</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.112</v>
+        <v>0.113</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
@@ -7359,31 +7359,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C46" t="n">
-        <v>0.226</v>
+        <v>0.212</v>
       </c>
       <c r="D46" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="E46" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="F46" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="G46" t="n">
-        <v>0.29</v>
+        <v>0.273</v>
       </c>
       <c r="H46" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="I46" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="J46" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -7401,22 +7401,22 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.129</v>
+        <v>0.121</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.129</v>
+        <v>0.121</v>
       </c>
       <c r="R46" t="n">
-        <v>0.194</v>
+        <v>0.182</v>
       </c>
       <c r="S46" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="T46" t="n">
         <v>-9</v>
       </c>
       <c r="U46" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -7428,10 +7428,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="AA46" t="n">
         <v>1</v>
@@ -7446,10 +7446,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="AG46" t="n">
         <v>0.5</v>
@@ -7464,21 +7464,21 @@
         <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.29</v>
+        <v>0.273</v>
       </c>
       <c r="AM46" t="n">
         <v>0.111</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>01:39</t>
+          <t>01:33</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>0.512</v>
+        <v>0.481</v>
       </c>
       <c r="AP46" t="n">
         <v>0.227</v>
@@ -7499,7 +7499,7 @@
         <v>0.25</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
       <c r="AW46" t="n">
         <v>0</v>
@@ -7518,40 +7518,40 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C47" t="n">
-        <v>0.519</v>
+        <v>0.552</v>
       </c>
       <c r="D47" t="n">
-        <v>0.037</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>0.074</v>
+        <v>0.103</v>
       </c>
       <c r="F47" t="n">
-        <v>0.148</v>
+        <v>0.138</v>
       </c>
       <c r="G47" t="n">
-        <v>0.444</v>
+        <v>0.448</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="K47" t="n">
-        <v>0.296</v>
+        <v>0.276</v>
       </c>
       <c r="L47" t="n">
-        <v>0.074</v>
+        <v>0.103</v>
       </c>
       <c r="M47" t="n">
-        <v>0.111</v>
+        <v>0.103</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -7560,22 +7560,22 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="R47" t="n">
-        <v>0.37</v>
+        <v>0.379</v>
       </c>
       <c r="S47" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="T47" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U47" t="n">
-        <v>0.111</v>
+        <v>0.103</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -7587,19 +7587,19 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.074</v>
+        <v>0.103</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AD47" t="n">
         <v>0.5</v>
@@ -7614,60 +7614,60 @@
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.222</v>
+        <v>0.241</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.222</v>
+        <v>0.207</v>
       </c>
       <c r="AM47" t="n">
         <v>0.333</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>02:42</t>
+          <t>02:56</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>0.588</v>
+        <v>0.617</v>
       </c>
       <c r="AP47" t="n">
         <v>0.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.47</v>
+        <v>0.474</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.882</v>
+        <v>0.895</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.063</v>
+        <v>0.056</v>
       </c>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.1</v>
+        <v>0.097</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.032</v>
+        <v>0.041</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.123</v>
+        <v>0.106</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="48">
@@ -7823,10 +7823,10 @@
         <v>0.017</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="49">
@@ -7982,10 +7982,10 @@
         <v>0.019</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="50">
@@ -7995,43 +7995,43 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C50" t="n">
-        <v>10.955</v>
+        <v>11.348</v>
       </c>
       <c r="D50" t="n">
-        <v>2.364</v>
+        <v>2.435</v>
       </c>
       <c r="E50" t="n">
-        <v>4.273</v>
+        <v>4.304</v>
       </c>
       <c r="F50" t="n">
-        <v>1.227</v>
+        <v>1.304</v>
       </c>
       <c r="G50" t="n">
-        <v>3.636</v>
+        <v>3.739</v>
       </c>
       <c r="H50" t="n">
-        <v>2.545</v>
+        <v>2.565</v>
       </c>
       <c r="I50" t="n">
-        <v>2.955</v>
+        <v>3.043</v>
       </c>
       <c r="J50" t="n">
-        <v>1.727</v>
+        <v>1.826</v>
       </c>
       <c r="K50" t="n">
-        <v>2.727</v>
+        <v>2.739</v>
       </c>
       <c r="L50" t="n">
-        <v>1.091</v>
+        <v>1.043</v>
       </c>
       <c r="M50" t="n">
-        <v>1.727</v>
+        <v>1.696</v>
       </c>
       <c r="N50" t="n">
-        <v>0.636</v>
+        <v>0.696</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -8043,108 +8043,108 @@
         <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>3.136</v>
+        <v>3.13</v>
       </c>
       <c r="S50" t="n">
-        <v>3.045</v>
+        <v>3.043</v>
       </c>
       <c r="T50" t="n">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="U50" t="n">
-        <v>1.591</v>
+        <v>1.739</v>
       </c>
       <c r="V50" t="n">
-        <v>1.318</v>
+        <v>1.348</v>
       </c>
       <c r="W50" t="n">
-        <v>1.182</v>
+        <v>1.217</v>
       </c>
       <c r="X50" t="n">
-        <v>0.773</v>
+        <v>0.783</v>
       </c>
       <c r="Y50" t="n">
-        <v>4.455</v>
+        <v>4.565</v>
       </c>
       <c r="Z50" t="n">
-        <v>5.545</v>
+        <v>5.696</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.803</v>
+        <v>0.802</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.364</v>
+        <v>0.348</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.136</v>
+        <v>1.087</v>
       </c>
       <c r="AD50" t="n">
         <v>0.32</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.091</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.545</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.167</v>
+        <v>0.154</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.273</v>
+        <v>0.261</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.727</v>
+        <v>0.696</v>
       </c>
       <c r="AJ50" t="n">
         <v>0.375</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.955</v>
+        <v>1.043</v>
       </c>
       <c r="AL50" t="n">
-        <v>2.909</v>
+        <v>3.043</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.328</v>
+        <v>0.343</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>11.209</v>
+        <v>11.383</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.532</v>
+        <v>0.546</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.595</v>
+        <v>0.605</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.977</v>
+        <v>0.997</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.322</v>
+        <v>0.319</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.864</v>
+        <v>0.913</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.239</v>
+        <v>0.241</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.074</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="51">
@@ -8154,156 +8154,156 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C51" t="n">
-        <v>4.889</v>
+        <v>5.737</v>
       </c>
       <c r="D51" t="n">
-        <v>0.833</v>
+        <v>0.947</v>
       </c>
       <c r="E51" t="n">
-        <v>2.278</v>
+        <v>2.316</v>
       </c>
       <c r="F51" t="n">
-        <v>0.667</v>
+        <v>0.842</v>
       </c>
       <c r="G51" t="n">
-        <v>1.889</v>
+        <v>2.105</v>
       </c>
       <c r="H51" t="n">
-        <v>1.222</v>
+        <v>1.316</v>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>1.632</v>
       </c>
       <c r="J51" t="n">
-        <v>0.5</v>
+        <v>0.526</v>
       </c>
       <c r="K51" t="n">
-        <v>2.944</v>
+        <v>3.211</v>
       </c>
       <c r="L51" t="n">
-        <v>1.111</v>
+        <v>1.053</v>
       </c>
       <c r="M51" t="n">
-        <v>0.722</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>0.389</v>
+        <v>0.368</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0.667</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.667</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="R51" t="n">
-        <v>2.111</v>
+        <v>2.158</v>
       </c>
       <c r="S51" t="n">
-        <v>1.333</v>
+        <v>1.421</v>
       </c>
       <c r="T51" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="U51" t="n">
-        <v>0.722</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="V51" t="n">
-        <v>0.889</v>
+        <v>0.842</v>
       </c>
       <c r="W51" t="n">
-        <v>0.333</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="X51" t="n">
-        <v>0.222</v>
+        <v>0.474</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.667</v>
+        <v>1.895</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.556</v>
+        <v>2.789</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.652</v>
+        <v>0.679</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.333</v>
+        <v>0.316</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.778</v>
+        <v>0.737</v>
       </c>
       <c r="AD51" t="n">
         <v>0.429</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.056</v>
+        <v>0.053</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.444</v>
+        <v>0.421</v>
       </c>
       <c r="AG51" t="n">
         <v>0.125</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.111</v>
+        <v>0.105</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.278</v>
+        <v>0.316</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.556</v>
+        <v>0.737</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.611</v>
+        <v>1.789</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.345</v>
+        <v>0.412</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>5.493</v>
+        <v>5.823</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.506</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AR51" t="n">
-        <v>0.89</v>
+        <v>0.985</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.121</v>
+        <v>0.117</v>
       </c>
       <c r="AT51" t="n">
-        <v>0.293</v>
+        <v>0.298</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.75</v>
+        <v>0.769</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.149</v>
+        <v>0.152</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.076</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AX51" t="n">
-        <v>0.194</v>
+        <v>0.204</v>
       </c>
       <c r="AY51" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="52">
@@ -8313,106 +8313,106 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C52" t="n">
-        <v>16.094</v>
+        <v>16.176</v>
       </c>
       <c r="D52" t="n">
-        <v>3.656</v>
+        <v>3.765</v>
       </c>
       <c r="E52" t="n">
-        <v>6.562</v>
+        <v>6.735</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>1.75</v>
+        <v>1.676</v>
       </c>
       <c r="H52" t="n">
-        <v>7.094</v>
+        <v>6.971</v>
       </c>
       <c r="I52" t="n">
-        <v>8.75</v>
+        <v>8.529</v>
       </c>
       <c r="J52" t="n">
-        <v>2.938</v>
+        <v>3.118</v>
       </c>
       <c r="K52" t="n">
         <v>4.5</v>
       </c>
       <c r="L52" t="n">
-        <v>1.938</v>
+        <v>2.059</v>
       </c>
       <c r="M52" t="n">
-        <v>1.094</v>
+        <v>1.118</v>
       </c>
       <c r="N52" t="n">
-        <v>0.969</v>
+        <v>0.971</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.781</v>
+        <v>1.794</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.781</v>
+        <v>1.794</v>
       </c>
       <c r="R52" t="n">
-        <v>1.656</v>
+        <v>1.618</v>
       </c>
       <c r="S52" t="n">
-        <v>7.188</v>
+        <v>7</v>
       </c>
       <c r="T52" t="n">
-        <v>817</v>
+        <v>880</v>
       </c>
       <c r="U52" t="n">
-        <v>2.219</v>
+        <v>2.412</v>
       </c>
       <c r="V52" t="n">
-        <v>2.531</v>
+        <v>2.441</v>
       </c>
       <c r="W52" t="n">
-        <v>1.031</v>
+        <v>1.029</v>
       </c>
       <c r="X52" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Y52" t="n">
-        <v>10.062</v>
+        <v>10.029</v>
       </c>
       <c r="Z52" t="n">
-        <v>13.125</v>
+        <v>13</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.767</v>
+        <v>0.771</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.625</v>
+        <v>0.647</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.906</v>
+        <v>1.971</v>
       </c>
       <c r="AD52" t="n">
         <v>0.328</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.281</v>
+        <v>0.294</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="AJ52" t="n">
         <v>0.154</v>
@@ -8421,48 +8421,48 @@
         <v>0.5</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.344</v>
+        <v>1.294</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.372</v>
+        <v>0.386</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>29:10</t>
+          <t>29:15</t>
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>13.944</v>
+        <v>13.959</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.541</v>
+        <v>0.547</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.662</v>
+        <v>0.665</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.154</v>
+        <v>1.159</v>
       </c>
       <c r="AS52" t="n">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
       <c r="AT52" t="n">
-        <v>0.853</v>
+        <v>0.829</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.649</v>
+        <v>1.738</v>
       </c>
       <c r="AV52" t="n">
         <v>0.22</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.077</v>
+        <v>0.082</v>
       </c>
       <c r="AX52" t="n">
         <v>0.173</v>
       </c>
       <c r="AY52" t="n">
-        <v>0.13</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="53">
@@ -8777,10 +8777,10 @@
         <v>0.098</v>
       </c>
       <c r="AX54" t="n">
-        <v>0.278</v>
+        <v>0.28</v>
       </c>
       <c r="AY54" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="55">
@@ -8790,16 +8790,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C55" t="n">
-        <v>4.696</v>
+        <v>4.8</v>
       </c>
       <c r="D55" t="n">
-        <v>1.565</v>
+        <v>1.6</v>
       </c>
       <c r="E55" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -8808,25 +8808,25 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1.565</v>
+        <v>1.6</v>
       </c>
       <c r="I55" t="n">
-        <v>2.217</v>
+        <v>2.24</v>
       </c>
       <c r="J55" t="n">
-        <v>0.478</v>
+        <v>0.48</v>
       </c>
       <c r="K55" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="L55" t="n">
-        <v>1.087</v>
+        <v>1.04</v>
       </c>
       <c r="M55" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="N55" t="n">
-        <v>1.652</v>
+        <v>1.6</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8838,49 +8838,49 @@
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>2.739</v>
+        <v>2.64</v>
       </c>
       <c r="S55" t="n">
-        <v>1.696</v>
+        <v>1.76</v>
       </c>
       <c r="T55" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="U55" t="n">
-        <v>0.435</v>
+        <v>0.4</v>
       </c>
       <c r="V55" t="n">
-        <v>1.435</v>
+        <v>1.4</v>
       </c>
       <c r="W55" t="n">
-        <v>0.174</v>
+        <v>0.16</v>
       </c>
       <c r="X55" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.696</v>
+        <v>3.76</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.776</v>
+        <v>0.787</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.217</v>
+        <v>0.2</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.478</v>
+        <v>0.44</v>
       </c>
       <c r="AD55" t="n">
         <v>0.455</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.174</v>
+        <v>0.16</v>
       </c>
       <c r="AG55" t="n">
         <v>0.25</v>
@@ -8905,38 +8905,38 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AO55" t="n">
         <v>4.106</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.735</v>
+        <v>0.755</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.756</v>
+        <v>0.773</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.144</v>
+        <v>1.169</v>
       </c>
       <c r="AS55" t="n">
         <v>0.244</v>
       </c>
       <c r="AT55" t="n">
-        <v>0.735</v>
+        <v>0.755</v>
       </c>
       <c r="AU55" t="n">
-        <v>0.478</v>
+        <v>0.48</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.15</v>
+        <v>0.153</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="AX55" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="AY55" t="n">
         <v>0.019</v>
@@ -9089,16 +9089,16 @@
         <v>0.615</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="AW56" t="n">
         <v>0.047</v>
       </c>
       <c r="AX56" t="n">
-        <v>0.145</v>
+        <v>0.146</v>
       </c>
       <c r="AY56" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="57">
@@ -9108,156 +9108,156 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C57" t="n">
-        <v>8.909000000000001</v>
+        <v>7.769</v>
       </c>
       <c r="D57" t="n">
-        <v>2.091</v>
+        <v>1.846</v>
       </c>
       <c r="E57" t="n">
-        <v>4.636</v>
+        <v>4.154</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>3.727</v>
+        <v>3.538</v>
       </c>
       <c r="H57" t="n">
-        <v>2.273</v>
+        <v>2</v>
       </c>
       <c r="I57" t="n">
-        <v>2.818</v>
+        <v>2.538</v>
       </c>
       <c r="J57" t="n">
-        <v>1.727</v>
+        <v>1.615</v>
       </c>
       <c r="K57" t="n">
-        <v>1.727</v>
+        <v>1.462</v>
       </c>
       <c r="L57" t="n">
-        <v>0.727</v>
+        <v>0.846</v>
       </c>
       <c r="M57" t="n">
-        <v>1.182</v>
+        <v>1.077</v>
       </c>
       <c r="N57" t="n">
-        <v>0.545</v>
+        <v>0.462</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.273</v>
+        <v>2.077</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.273</v>
+        <v>2.077</v>
       </c>
       <c r="R57" t="n">
-        <v>2.455</v>
+        <v>2.462</v>
       </c>
       <c r="S57" t="n">
-        <v>2.636</v>
+        <v>2.462</v>
       </c>
       <c r="T57" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U57" t="n">
-        <v>1.727</v>
+        <v>1.615</v>
       </c>
       <c r="V57" t="n">
-        <v>0.727</v>
+        <v>0.615</v>
       </c>
       <c r="W57" t="n">
-        <v>0.455</v>
+        <v>0.385</v>
       </c>
       <c r="X57" t="n">
-        <v>0.364</v>
+        <v>0.308</v>
       </c>
       <c r="Y57" t="n">
-        <v>3.909</v>
+        <v>3.462</v>
       </c>
       <c r="Z57" t="n">
-        <v>5.273</v>
+        <v>4.692</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.741</v>
+        <v>0.738</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.364</v>
+        <v>0.308</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.455</v>
+        <v>1.308</v>
       </c>
       <c r="AD57" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AJ57" t="n">
         <v>0.25</v>
       </c>
-      <c r="AE57" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.286</v>
-      </c>
       <c r="AK57" t="n">
-        <v>0.636</v>
+        <v>0.538</v>
       </c>
       <c r="AL57" t="n">
-        <v>3.091</v>
+        <v>2.923</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.206</v>
+        <v>0.184</v>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="AO57" t="n">
-        <v>11.876</v>
+        <v>10.886</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.397</v>
+        <v>0.375</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.464</v>
+        <v>0.441</v>
       </c>
       <c r="AR57" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="AS57" t="n">
         <v>0.191</v>
       </c>
       <c r="AT57" t="n">
-        <v>0.272</v>
+        <v>0.26</v>
       </c>
       <c r="AU57" t="n">
-        <v>0.76</v>
+        <v>0.778</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.233</v>
+        <v>0.224</v>
       </c>
       <c r="AW57" t="n">
-        <v>0.036</v>
+        <v>0.044</v>
       </c>
       <c r="AX57" t="n">
-        <v>0.082</v>
+        <v>0.073</v>
       </c>
       <c r="AY57" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="58">
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -9294,10 +9294,10 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1.375</v>
+        <v>1.324</v>
       </c>
       <c r="L58" t="n">
-        <v>1.531</v>
+        <v>1.529</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -9309,13 +9309,13 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1.188</v>
+        <v>1.206</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -9426,150 +9426,150 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C59" t="n">
-        <v>82.71899999999999</v>
+        <v>83.765</v>
       </c>
       <c r="D59" t="n">
-        <v>18.625</v>
+        <v>19.029</v>
       </c>
       <c r="E59" t="n">
-        <v>35.906</v>
+        <v>36.088</v>
       </c>
       <c r="F59" t="n">
-        <v>8.156000000000001</v>
+        <v>8.353</v>
       </c>
       <c r="G59" t="n">
-        <v>24.406</v>
+        <v>24.529</v>
       </c>
       <c r="H59" t="n">
-        <v>21</v>
+        <v>20.647</v>
       </c>
       <c r="I59" t="n">
-        <v>27.094</v>
+        <v>26.735</v>
       </c>
       <c r="J59" t="n">
-        <v>14.906</v>
+        <v>15.294</v>
       </c>
       <c r="K59" t="n">
-        <v>24.094</v>
+        <v>23.853</v>
       </c>
       <c r="L59" t="n">
-        <v>10</v>
+        <v>9.912000000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>6.781</v>
+        <v>6.765</v>
       </c>
       <c r="N59" t="n">
-        <v>6.406</v>
+        <v>6.235</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>14.938</v>
+        <v>14.824</v>
       </c>
       <c r="Q59" t="n">
-        <v>13.75</v>
+        <v>13.618</v>
       </c>
       <c r="R59" t="n">
-        <v>23.406</v>
+        <v>23.147</v>
       </c>
       <c r="S59" t="n">
-        <v>23.375</v>
+        <v>23.206</v>
       </c>
       <c r="T59" t="n">
-        <v>2890</v>
+        <v>3119</v>
       </c>
       <c r="U59" t="n">
-        <v>10.344</v>
+        <v>10.382</v>
       </c>
       <c r="V59" t="n">
-        <v>9.75</v>
+        <v>9.529</v>
       </c>
       <c r="W59" t="n">
-        <v>5.281</v>
+        <v>5.647</v>
       </c>
       <c r="X59" t="n">
-        <v>3.5</v>
+        <v>3.706</v>
       </c>
       <c r="Y59" t="n">
-        <v>33.719</v>
+        <v>33.765</v>
       </c>
       <c r="Z59" t="n">
-        <v>45.406</v>
+        <v>45.324</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="AB59" t="n">
-        <v>3.688</v>
+        <v>3.706</v>
       </c>
       <c r="AC59" t="n">
-        <v>10.938</v>
+        <v>10.853</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="AE59" t="n">
-        <v>2.219</v>
+        <v>2.206</v>
       </c>
       <c r="AF59" t="n">
-        <v>6.656</v>
+        <v>6.647</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.333</v>
+        <v>0.332</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.562</v>
+        <v>1.5</v>
       </c>
       <c r="AI59" t="n">
-        <v>4.375</v>
+        <v>4.294</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.357</v>
+        <v>0.349</v>
       </c>
       <c r="AK59" t="n">
-        <v>6.594</v>
+        <v>6.853</v>
       </c>
       <c r="AL59" t="n">
-        <v>20.031</v>
+        <v>20.235</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.329</v>
+        <v>0.339</v>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>200:46</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO59" t="n">
-        <v>87.17100000000001</v>
+        <v>87.205</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.512</v>
+        <v>0.521</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.573</v>
+        <v>0.579</v>
       </c>
       <c r="AR59" t="n">
-        <v>0.949</v>
+        <v>0.961</v>
       </c>
       <c r="AS59" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="AT59" t="n">
-        <v>0.348</v>
+        <v>0.341</v>
       </c>
       <c r="AU59" t="n">
-        <v>0.998</v>
+        <v>1.032</v>
       </c>
       <c r="AV59" t="n">
         <v>0.2</v>
       </c>
       <c r="AW59" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="AX59" t="n">
         <v>0.134</v>
@@ -9585,144 +9585,144 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C60" t="n">
-        <v>91.688</v>
+        <v>92.735</v>
       </c>
       <c r="D60" t="n">
-        <v>22.438</v>
+        <v>22.529</v>
       </c>
       <c r="E60" t="n">
-        <v>38.469</v>
+        <v>38.618</v>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>10.294</v>
       </c>
       <c r="G60" t="n">
-        <v>28.625</v>
+        <v>28.735</v>
       </c>
       <c r="H60" t="n">
-        <v>16.812</v>
+        <v>16.794</v>
       </c>
       <c r="I60" t="n">
-        <v>22.812</v>
+        <v>22.559</v>
       </c>
       <c r="J60" t="n">
-        <v>17.75</v>
+        <v>17.912</v>
       </c>
       <c r="K60" t="n">
-        <v>24.781</v>
+        <v>24.618</v>
       </c>
       <c r="L60" t="n">
-        <v>11.812</v>
+        <v>11.824</v>
       </c>
       <c r="M60" t="n">
-        <v>7.719</v>
+        <v>7.559</v>
       </c>
       <c r="N60" t="n">
-        <v>6.594</v>
+        <v>6.441</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>12.094</v>
+        <v>11.941</v>
       </c>
       <c r="Q60" t="n">
-        <v>11.031</v>
+        <v>10.912</v>
       </c>
       <c r="R60" t="n">
-        <v>23.531</v>
+        <v>23.382</v>
       </c>
       <c r="S60" t="n">
-        <v>23.062</v>
+        <v>22.765</v>
       </c>
       <c r="T60" t="n">
-        <v>3428</v>
+        <v>3680</v>
       </c>
       <c r="U60" t="n">
-        <v>11.969</v>
+        <v>11.912</v>
       </c>
       <c r="V60" t="n">
-        <v>11.906</v>
+        <v>12</v>
       </c>
       <c r="W60" t="n">
-        <v>7</v>
+        <v>6.824</v>
       </c>
       <c r="X60" t="n">
-        <v>4.188</v>
+        <v>4.059</v>
       </c>
       <c r="Y60" t="n">
-        <v>31.719</v>
+        <v>31.853</v>
       </c>
       <c r="Z60" t="n">
-        <v>42.875</v>
+        <v>42.824</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.74</v>
+        <v>0.744</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.938</v>
+        <v>4.824</v>
       </c>
       <c r="AC60" t="n">
-        <v>10.719</v>
+        <v>10.676</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.461</v>
+        <v>0.452</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.594</v>
+        <v>2.647</v>
       </c>
       <c r="AF60" t="n">
-        <v>7.688</v>
+        <v>7.676</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.337</v>
+        <v>0.345</v>
       </c>
       <c r="AH60" t="n">
-        <v>2.75</v>
+        <v>2.735</v>
       </c>
       <c r="AI60" t="n">
-        <v>6.75</v>
+        <v>6.647</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.407</v>
+        <v>0.412</v>
       </c>
       <c r="AK60" t="n">
-        <v>7.25</v>
+        <v>7.559</v>
       </c>
       <c r="AL60" t="n">
-        <v>21.875</v>
+        <v>22.088</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.331</v>
+        <v>0.342</v>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>200:46</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO60" t="n">
-        <v>89.22499999999999</v>
+        <v>89.22</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.594</v>
+        <v>0.6</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.028</v>
+        <v>1.039</v>
       </c>
       <c r="AS60" t="n">
-        <v>0.136</v>
+        <v>0.134</v>
       </c>
       <c r="AT60" t="n">
-        <v>0.251</v>
+        <v>0.249</v>
       </c>
       <c r="AU60" t="n">
-        <v>1.468</v>
+        <v>1.5</v>
       </c>
       <c r="AV60" t="n">
         <v>0.205</v>
